--- a/DatasetUnical/Results/dlinear-predprod/analysis_dlinear-predprod.xlsx
+++ b/DatasetUnical/Results/dlinear-predprod/analysis_dlinear-predprod.xlsx
@@ -909,11 +909,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>8.4</v>
+        <v>703.74</v>
       </c>
     </row>
     <row r="9">
@@ -958,14 +958,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>703.74</v>
       </c>
     </row>
     <row r="10">
@@ -2170,11 +2162,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.26</v>
+        <v>708.8</v>
       </c>
     </row>
     <row r="9">
@@ -2219,14 +2211,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>708.8</v>
       </c>
     </row>
     <row r="10">
@@ -3431,11 +3415,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.27</v>
+        <v>652.34</v>
       </c>
     </row>
     <row r="9">
@@ -3480,14 +3464,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>652.34</v>
       </c>
     </row>
     <row r="10">
@@ -4692,11 +4668,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.83</v>
+        <v>785.16</v>
       </c>
     </row>
     <row r="9">
@@ -4741,14 +4717,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>785.16</v>
       </c>
     </row>
     <row r="10">
@@ -5953,11 +5921,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.31</v>
+        <v>754.65</v>
       </c>
     </row>
     <row r="9">
@@ -6002,14 +5970,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>754.65</v>
       </c>
     </row>
     <row r="10">
@@ -7214,11 +7174,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.27</v>
+        <v>761.5599999999999</v>
       </c>
     </row>
     <row r="9">
@@ -7263,14 +7223,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>761.5599999999999</v>
       </c>
     </row>
     <row r="10">
@@ -8475,11 +8427,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.27</v>
+        <v>711.22</v>
       </c>
     </row>
     <row r="9">
@@ -8524,14 +8476,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>711.22</v>
       </c>
     </row>
     <row r="10">
@@ -9736,11 +9680,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.28</v>
+        <v>684.0700000000001</v>
       </c>
     </row>
     <row r="9">
@@ -9785,14 +9729,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>684.0700000000001</v>
       </c>
     </row>
     <row r="10">
@@ -10997,11 +10933,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="9">
@@ -11046,14 +10982,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>0.08</v>
       </c>
     </row>
     <row r="10">
@@ -12258,11 +12186,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.28</v>
+        <v>702.5599999999999</v>
       </c>
     </row>
     <row r="9">
@@ -12307,14 +12235,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>702.5599999999999</v>
       </c>
     </row>
     <row r="10">
@@ -13519,7 +13439,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -13568,14 +13488,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -14780,11 +14692,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.32</v>
+        <v>720.99</v>
       </c>
     </row>
     <row r="9">
@@ -14829,14 +14741,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>720.99</v>
       </c>
     </row>
     <row r="10">
@@ -16041,11 +15945,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.17</v>
+        <v>793.55</v>
       </c>
     </row>
     <row r="9">
@@ -16090,14 +15994,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>793.55</v>
       </c>
     </row>
     <row r="10">
@@ -17302,11 +17198,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>678.04</v>
       </c>
     </row>
     <row r="9">
@@ -17351,14 +17247,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>678.04</v>
       </c>
     </row>
     <row r="10">
@@ -18563,11 +18451,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.27</v>
+        <v>690.39</v>
       </c>
     </row>
     <row r="9">
@@ -18612,14 +18500,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>690.39</v>
       </c>
     </row>
     <row r="10">
@@ -19824,11 +19704,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.28</v>
+        <v>694.6900000000001</v>
       </c>
     </row>
     <row r="9">
@@ -19873,14 +19753,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>694.6900000000001</v>
       </c>
     </row>
     <row r="10">
@@ -21085,11 +20957,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>739.11</v>
       </c>
     </row>
     <row r="9">
@@ -21134,14 +21006,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>739.11</v>
       </c>
     </row>
     <row r="10">
@@ -22346,11 +22210,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.27</v>
+        <v>771.47</v>
       </c>
     </row>
     <row r="9">
@@ -22395,14 +22259,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>771.47</v>
       </c>
     </row>
     <row r="10">
@@ -23607,11 +23463,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.22</v>
+        <v>775.4299999999999</v>
       </c>
     </row>
     <row r="9">
@@ -23656,14 +23512,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>775.4299999999999</v>
       </c>
     </row>
     <row r="10">
@@ -24868,11 +24716,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>797.58</v>
       </c>
     </row>
     <row r="9">
@@ -24917,14 +24765,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>797.58</v>
       </c>
     </row>
     <row r="10">
@@ -26129,11 +25969,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.24</v>
+        <v>746.67</v>
       </c>
     </row>
     <row r="9">
@@ -26178,14 +26018,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>746.67</v>
       </c>
     </row>
     <row r="10">
@@ -27390,11 +27222,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>752.8</v>
       </c>
     </row>
     <row r="9">
@@ -27439,14 +27271,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>752.8</v>
       </c>
     </row>
     <row r="10">
@@ -28651,11 +28475,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.26</v>
+        <v>660.79</v>
       </c>
     </row>
     <row r="9">
@@ -28700,14 +28524,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>660.79</v>
       </c>
     </row>
     <row r="10">
@@ -29912,11 +29728,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>716.95</v>
       </c>
     </row>
     <row r="9">
@@ -29961,14 +29777,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>716.95</v>
       </c>
     </row>
     <row r="10">
@@ -31173,11 +30981,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.27</v>
+        <v>703.76</v>
       </c>
     </row>
     <row r="9">
@@ -31222,14 +31030,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>703.76</v>
       </c>
     </row>
     <row r="10">
@@ -32434,11 +32234,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>741.75</v>
       </c>
     </row>
     <row r="9">
@@ -32483,14 +32283,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>741.75</v>
       </c>
     </row>
     <row r="10">
@@ -33695,11 +33487,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.27</v>
+        <v>833.04</v>
       </c>
     </row>
     <row r="9">
@@ -33744,14 +33536,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>833.04</v>
       </c>
     </row>
     <row r="10">
@@ -34956,7 +34740,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -35005,14 +34789,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -36217,11 +35993,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.14</v>
+        <v>864.12</v>
       </c>
     </row>
     <row r="9">
@@ -36266,14 +36042,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>864.12</v>
       </c>
     </row>
     <row r="10">
@@ -37478,11 +37246,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.22</v>
+        <v>767.6</v>
       </c>
     </row>
     <row r="9">
@@ -37527,14 +37295,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>767.6</v>
       </c>
     </row>
     <row r="10">
@@ -38739,11 +38499,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.22</v>
+        <v>737.45</v>
       </c>
     </row>
     <row r="9">
@@ -38788,14 +38548,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>737.45</v>
       </c>
     </row>
     <row r="10">
@@ -40000,11 +39752,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.17</v>
+        <v>728.88</v>
       </c>
     </row>
     <row r="9">
@@ -40049,14 +39801,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>728.88</v>
       </c>
     </row>
     <row r="10">
@@ -41261,11 +41005,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.13</v>
+        <v>766.72</v>
       </c>
     </row>
     <row r="9">
@@ -41310,14 +41054,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>766.72</v>
       </c>
     </row>
     <row r="10">
@@ -42522,11 +42258,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>700.73</v>
       </c>
     </row>
     <row r="9">
@@ -42571,14 +42307,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>700.73</v>
       </c>
     </row>
     <row r="10">
@@ -43783,11 +43511,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.27</v>
+        <v>729.25</v>
       </c>
     </row>
     <row r="9">
@@ -43832,14 +43560,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>729.25</v>
       </c>
     </row>
     <row r="10">
@@ -45044,11 +44764,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.32</v>
+        <v>902.61</v>
       </c>
     </row>
     <row r="9">
@@ -45093,14 +44813,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>902.61</v>
       </c>
     </row>
     <row r="10">
@@ -46305,7 +46017,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -46354,14 +46066,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -47566,11 +47270,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.24</v>
+        <v>820.3</v>
       </c>
     </row>
     <row r="9">
@@ -47615,14 +47319,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>820.3</v>
       </c>
     </row>
     <row r="10">
@@ -48827,11 +48523,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.11</v>
+        <v>850.63</v>
       </c>
     </row>
     <row r="9">
@@ -48876,14 +48572,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>850.63</v>
       </c>
     </row>
     <row r="10">
@@ -50088,11 +49776,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.18</v>
+        <v>828.33</v>
       </c>
     </row>
     <row r="9">
@@ -50137,14 +49825,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>828.33</v>
       </c>
     </row>
     <row r="10">
@@ -51349,11 +51029,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.14</v>
+        <v>803.65</v>
       </c>
     </row>
     <row r="9">
@@ -51398,14 +51078,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>803.65</v>
       </c>
     </row>
     <row r="10">
@@ -52610,11 +52282,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.22</v>
+        <v>770</v>
       </c>
     </row>
     <row r="9">
@@ -52659,14 +52331,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>770</v>
       </c>
     </row>
     <row r="10">
@@ -53871,11 +53535,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>777.71</v>
       </c>
     </row>
     <row r="9">
@@ -53920,14 +53584,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>777.71</v>
       </c>
     </row>
     <row r="10">
@@ -55132,11 +54788,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.21</v>
+        <v>772.0700000000001</v>
       </c>
     </row>
     <row r="9">
@@ -55181,14 +54837,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>772.0700000000001</v>
       </c>
     </row>
     <row r="10">
@@ -56393,11 +56041,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.26</v>
+        <v>690.8200000000001</v>
       </c>
     </row>
     <row r="9">
@@ -56442,14 +56090,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>690.8200000000001</v>
       </c>
     </row>
     <row r="10">
@@ -57654,11 +57294,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.22</v>
+        <v>777.54</v>
       </c>
     </row>
     <row r="9">
@@ -57703,14 +57343,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>777.54</v>
       </c>
     </row>
     <row r="10">
@@ -58915,11 +58547,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>798.39</v>
       </c>
     </row>
     <row r="9">
@@ -58964,14 +58596,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>798.39</v>
       </c>
     </row>
     <row r="10">
@@ -60176,11 +59800,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.13</v>
+        <v>859.27</v>
       </c>
     </row>
     <row r="9">
@@ -60225,14 +59849,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>859.27</v>
       </c>
     </row>
     <row r="10">
@@ -61173,11 +60789,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.26</v>
+        <v>673.99</v>
       </c>
     </row>
     <row r="9">
@@ -61222,14 +60838,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>673.99</v>
       </c>
     </row>
     <row r="10">
@@ -62434,11 +62042,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.28</v>
+        <v>622.9400000000001</v>
       </c>
     </row>
     <row r="9">
@@ -62483,14 +62091,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>622.9400000000001</v>
       </c>
     </row>
     <row r="10">
@@ -63695,11 +63295,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.27</v>
+        <v>655.04</v>
       </c>
     </row>
     <row r="9">
@@ -63744,14 +63344,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>655.04</v>
       </c>
     </row>
     <row r="10">
@@ -64956,11 +64548,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>727.39</v>
       </c>
     </row>
     <row r="9">
@@ -65005,14 +64597,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>727.39</v>
       </c>
     </row>
     <row r="10">

--- a/DatasetUnical/Results/dlinear-predprod/analysis_dlinear-predprod.xlsx
+++ b/DatasetUnical/Results/dlinear-predprod/analysis_dlinear-predprod.xlsx
@@ -909,11 +909,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>703.74</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -957,6 +959,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -2162,11 +2173,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>708.8</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2210,6 +2223,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -3415,11 +3437,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>652.34</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -3463,6 +3487,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -4668,11 +4701,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>785.16</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -4716,6 +4751,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -5921,11 +5965,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>754.65</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -5969,6 +6015,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -7174,11 +7229,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>761.5599999999999</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -7222,6 +7279,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -8427,11 +8493,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>711.22</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -8475,6 +8543,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -9680,11 +9757,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>684.0700000000001</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -9728,6 +9807,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -10933,11 +11021,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>0.08</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -10981,6 +11071,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -12186,11 +12285,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>702.5599999999999</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -12234,6 +12335,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -13439,11 +13549,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>0.03</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -13487,6 +13599,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -14692,11 +14813,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>720.99</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -14740,6 +14863,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -15945,11 +16077,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>793.55</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -15993,6 +16127,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -17198,11 +17341,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>678.04</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -17246,6 +17391,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -18451,11 +18605,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>690.39</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -18499,6 +18655,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -19704,11 +19869,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>694.6900000000001</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -19752,6 +19919,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -20957,11 +21133,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>739.11</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -21005,6 +21183,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -22210,11 +22397,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>771.47</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -22258,6 +22447,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -23463,11 +23661,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>775.4299999999999</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -23511,6 +23711,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -24716,11 +24925,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>797.58</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -24764,6 +24975,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -25969,11 +26189,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>746.67</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -26017,6 +26239,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -27222,11 +27453,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>752.8</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -27270,6 +27503,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -28475,11 +28717,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>660.79</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -28523,6 +28767,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -29728,11 +29981,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>716.95</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -29776,6 +30031,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -30981,11 +31245,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>703.76</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -31029,6 +31295,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -32234,11 +32509,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>741.75</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -32282,6 +32559,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -33487,11 +33773,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>833.04</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -33535,6 +33823,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -34740,11 +35037,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>0.03</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -34788,6 +35087,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -35993,11 +36301,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>864.12</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -36041,6 +36351,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -37246,11 +37565,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>767.6</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -37294,6 +37615,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -38499,11 +38829,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>737.45</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -38547,6 +38879,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -39752,11 +40093,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>728.88</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -39800,6 +40143,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -41005,11 +41357,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>766.72</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -41053,6 +41407,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -42258,11 +42621,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>700.73</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -42306,6 +42671,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -43511,11 +43885,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>729.25</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -43559,6 +43935,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -44764,11 +45149,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>902.61</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -44812,6 +45199,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -46017,11 +46413,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>0.03</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -46065,6 +46463,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -47270,11 +47677,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>820.3</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -47318,6 +47727,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -48523,11 +48941,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>850.63</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -48571,6 +48991,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -49776,11 +50205,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>828.33</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -49824,6 +50255,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -51029,11 +51469,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>803.65</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -51077,6 +51519,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -52282,11 +52733,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>770</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -52330,6 +52783,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -53535,11 +53997,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>777.71</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -53583,6 +54047,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -54788,11 +55261,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>772.0700000000001</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -54836,6 +55311,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -56041,11 +56525,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>690.8200000000001</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -56089,6 +56575,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -57294,11 +57789,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>777.54</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -57342,6 +57839,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -58547,11 +59053,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>798.39</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -58595,6 +59103,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -59800,11 +60317,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>859.27</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -59848,6 +60367,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -60789,11 +61317,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>673.99</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -60837,6 +61367,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -62042,11 +62581,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>622.9400000000001</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -62090,6 +62631,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -63295,11 +63845,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>655.04</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -63343,6 +63895,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
@@ -64548,11 +65109,13 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>727.39</v>
+          <t xml:space="preserve">Time Last Answer (seconds): </t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -64596,6 +65159,15 @@
       </c>
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
+        <v/>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time Last Answer (minutes): </t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>W8/60</f>
         <v/>
       </c>
     </row>
